--- a/Data kalibrasi suhu/data_kalibrasi.xlsx
+++ b/Data kalibrasi suhu/data_kalibrasi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\nopi cakep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1158D10-8FC5-450D-BAE5-F29517A61F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01B002EF-8FBC-4745-9123-62B1C8695543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4365" yWindow="4365" windowWidth="21600" windowHeight="11835" xr2:uid="{4C600840-4383-48AF-B7E5-5373576E3FBA}"/>
   </bookViews>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7A9C46-8DCB-40FE-8CF6-0556CF033293}">
-  <dimension ref="A2:D101"/>
+  <dimension ref="A2:D102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1484,11 +1484,11 @@
         <v>20</v>
       </c>
       <c r="C68">
-        <f t="shared" ref="C68:C101" si="2">100-ABS((B68-A68)/A68)*100</f>
+        <f t="shared" ref="C68:C102" si="2">100-ABS((B68-A68)/A68)*100</f>
         <v>98.98989898989899</v>
       </c>
       <c r="D68">
-        <f t="shared" ref="D68:D101" si="3">ABS((B68-A68)/A68)*100</f>
+        <f t="shared" ref="D68:D102" si="3">ABS((B68-A68)/A68)*100</f>
         <v>1.0101010101010066</v>
       </c>
     </row>
@@ -2016,6 +2016,22 @@
         <v>98.98989898989899</v>
       </c>
       <c r="D101">
+        <f t="shared" si="3"/>
+        <v>1.0101010101010066</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>19.8</v>
+      </c>
+      <c r="B102">
+        <v>20</v>
+      </c>
+      <c r="C102">
+        <f t="shared" si="2"/>
+        <v>98.98989898989899</v>
+      </c>
+      <c r="D102">
         <f t="shared" si="3"/>
         <v>1.0101010101010066</v>
       </c>
